--- a/business_forms/030_driving_policy_acknowledgment--business_forms.xlsx
+++ b/business_forms/030_driving_policy_acknowledgment--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_read_the_driving_policy_and_i_understand_its_requirements.'}</t>
+          <t>i_have_read_the_driving_policy_and_i_understand_its_requirements.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I have read the driving policy and I understand its requirements.'}</t>
+          <t>I have read the driving policy and I understand its requirements.</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_not_read_the_driving_policy_and_i_do_not_understand_its_requirements.'}</t>
+          <t>i_have_not_read_the_driving_policy_and_i_do_not_understand_its_requirements.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'I have not read the driving policy and I do not understand its requirements.'}</t>
+          <t>I have not read the driving policy and I do not understand its requirements.</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_the_owner_or_operator_of_the_vehicle.'}</t>
+          <t>i_am_the_owner_or_operator_of_the_vehicle.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'I am the owner or operator of the vehicle.'}</t>
+          <t>I am the owner or operator of the vehicle.</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_the_passenger_of_the_vehicle.'}</t>
+          <t>i_am_the_passenger_of_the_vehicle.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I am the passenger of the vehicle.'}</t>
+          <t>I am the passenger of the vehicle.</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_passenger_of_the_vehicle.'}</t>
+          <t>i_am_a_passenger_of_the_vehicle.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'I am a passenger of the vehicle.'}</t>
+          <t>I am a passenger of the vehicle.</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'primary_contact_method'}</t>
+          <t>primary_contact_method</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Primary contact method'}</t>
+          <t>Primary contact method</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'secondary_contact_method'}</t>
+          <t>secondary_contact_method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Secondary contact method'}</t>
+          <t>Secondary contact method</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'emergency_contact_method'}</t>
+          <t>emergency_contact_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Emergency contact method'}</t>
+          <t>Emergency contact method</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'toyota'}</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Toyota'}</t>
+          <t>Toyota</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'honda'}</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Honda'}</t>
+          <t>Honda</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'ford'}</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Ford'}</t>
+          <t>Ford</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'corolla'}</t>
+          <t>corolla</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Corolla'}</t>
+          <t>Corolla</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'civic'}</t>
+          <t>civic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Civic'}</t>
+          <t>Civic</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'f150'}</t>
+          <t>f150</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'F150'}</t>
+          <t>F150</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'wa'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'WA'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'fl'}</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'FL'}</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_specified'}</t>
+          <t>not_specified</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not Specified'}</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'specified'}</t>
+          <t>specified</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Specified'}</t>
+          <t>Specified</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vehicle_registration_expiration_choices</t>
+          <t>vehicle_color_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'specified'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Specified'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'red'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Red'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'blue'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Blue'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vehicle_color_choices</t>
+          <t>emergency_contact_method_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'green'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Green'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>emergency_contact_method_choices</t>
+          <t>emergency_contact_person_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'sms'}</t>
+          <t>primary_contact_person</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'SMS'}</t>
+          <t>Primary contact person</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'primary_contact_person'}</t>
+          <t>secondary_contact_person</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Primary contact person'}</t>
+          <t>Secondary contact person</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'secondary_contact_person'}</t>
+          <t>tertiary_contact_person</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Secondary contact person'}</t>
+          <t>Tertiary contact person</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>emergency_contact_person_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'tertiary_contact_person'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Tertiary contact person'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>vehicle_status_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'sms'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'SMS'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vehicle_status_choices</t>
+          <t>vehicle_type_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'car'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Car'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'truck'}</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Truck'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>vehicle_type_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'van'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'Van'}</t>
+          <t>Van</t>
         </is>
       </c>
     </row>
